--- a/request_forms/004_elderly_meals_request_form--request_forms.xlsx
+++ b/request_forms/004_elderly_meals_request_form--request_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1198,7 +1198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1566,17 +1566,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>special_diet_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cash</t>
+          <t>online_payment</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Online Payment</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>online_payment</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Online Payment</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1622,27 +1622,10 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>payment_method_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>credit_card</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
         <is>
           <t>Credit Card</t>
         </is>
